--- a/assets/data/imf/excel/ove_pib_fmi_ngdp_precios_corrientes_moneda_nacional.xlsx
+++ b/assets/data/imf/excel/ove_pib_fmi_ngdp_precios_corrientes_moneda_nacional.xlsx
@@ -1497,7 +1497,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-25</t>
         </is>
       </c>
     </row>

--- a/assets/data/imf/excel/ove_pib_fmi_ngdp_precios_corrientes_moneda_nacional.xlsx
+++ b/assets/data/imf/excel/ove_pib_fmi_ngdp_precios_corrientes_moneda_nacional.xlsx
@@ -1497,7 +1497,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>

--- a/assets/data/imf/excel/ove_pib_fmi_ngdp_precios_corrientes_moneda_nacional.xlsx
+++ b/assets/data/imf/excel/ove_pib_fmi_ngdp_precios_corrientes_moneda_nacional.xlsx
@@ -1497,7 +1497,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>

--- a/assets/data/imf/excel/ove_pib_fmi_ngdp_precios_corrientes_moneda_nacional.xlsx
+++ b/assets/data/imf/excel/ove_pib_fmi_ngdp_precios_corrientes_moneda_nacional.xlsx
@@ -1497,7 +1497,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>

--- a/assets/data/imf/excel/ove_pib_fmi_ngdp_precios_corrientes_moneda_nacional.xlsx
+++ b/assets/data/imf/excel/ove_pib_fmi_ngdp_precios_corrientes_moneda_nacional.xlsx
@@ -1497,7 +1497,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
